--- a/до войны/до_войны_подписи_текст.xlsx
+++ b/до войны/до_войны_подписи_текст.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LDK99\Desktop\PeterhofParts\до войны\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Disk E\arhiv_site\Петергоф_выкладка\до войны\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A91922C-6F25-4D8C-A306-84B4A7656348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBCC6AB-964A-4463-BC97-4F9F86765FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="690" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2440" yWindow="0" windowWidth="33990" windowHeight="21140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -351,7 +351,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -630,13 +630,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -644,12 +644,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
@@ -657,7 +657,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
@@ -665,7 +665,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>35</v>
       </c>
@@ -673,7 +673,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -681,7 +681,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>39</v>
       </c>
@@ -689,7 +689,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>41</v>
       </c>
@@ -697,7 +697,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
@@ -705,7 +705,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>47</v>
       </c>
@@ -713,7 +713,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>49</v>
       </c>
@@ -721,7 +721,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>51</v>
       </c>
@@ -729,7 +729,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>52</v>
       </c>
@@ -737,7 +737,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>53</v>
       </c>
@@ -745,7 +745,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>57</v>
       </c>
@@ -753,7 +753,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>61</v>
       </c>
@@ -761,7 +761,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>63</v>
       </c>
@@ -769,7 +769,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>65</v>
       </c>
@@ -777,7 +777,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>67</v>
       </c>
@@ -785,7 +785,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>69</v>
       </c>
@@ -793,7 +793,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>71</v>
       </c>
@@ -801,7 +801,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>73</v>
       </c>
@@ -809,7 +809,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>59</v>
       </c>
@@ -817,7 +817,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>45</v>
       </c>
@@ -825,7 +825,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -833,7 +833,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>15</v>
       </c>
@@ -841,7 +841,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>7</v>
       </c>
@@ -849,7 +849,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>18</v>
       </c>
@@ -857,7 +857,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>3</v>
       </c>
@@ -865,7 +865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>5</v>
       </c>
@@ -873,7 +873,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
@@ -881,7 +881,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>13</v>
       </c>
@@ -889,7 +889,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>19</v>
       </c>
@@ -897,7 +897,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>21</v>
       </c>
@@ -905,7 +905,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>23</v>
       </c>
@@ -913,7 +913,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>25</v>
       </c>
@@ -921,7 +921,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>27</v>
       </c>
@@ -929,7 +929,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>29</v>
       </c>
@@ -939,6 +939,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>